--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1cn.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="1012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="1013">
   <si>
     <t>PE</t>
   </si>
@@ -4043,6 +4043,10 @@
   </si>
   <si>
     <t>利润</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4642,7 +4646,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4870,6 +4874,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4879,7 +4886,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5107,6 +5114,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>152000</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>154000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5149,7 +5159,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5377,6 +5387,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5386,7 +5399,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>2000.0000000000002</c:v>
                 </c:pt>
@@ -5614,6 +5627,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>237913.37769723308</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>252095.05628541086</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5656,7 +5672,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5884,6 +5900,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5893,7 +5912,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6121,6 +6140,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>85913.377697233082</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>98095.056285410858</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6142,11 +6164,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="305140480"/>
-        <c:axId val="305142016"/>
+        <c:axId val="460540544"/>
+        <c:axId val="460558720"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="305140480"/>
+        <c:axId val="460540544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6189,14 +6211,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="305142016"/>
+        <c:crossAx val="460558720"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="305142016"/>
+        <c:axId val="460558720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6247,7 +6269,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="305140480"/>
+        <c:crossAx val="460540544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6653,7 +6675,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB78"/>
+  <dimension ref="A1:AB79"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -6712,7 +6734,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -6751,25 +6773,25 @@
       </c>
       <c r="J3" s="6"/>
       <c r="L3" s="26" t="s">
-        <v>997</v>
+        <v>1006</v>
       </c>
       <c r="M3" s="27" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="N3" s="27" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="O3" s="27" t="s">
         <v>1004</v>
       </c>
       <c r="P3" s="27" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="Q3" s="27" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="R3" s="27" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="T3" s="23">
         <v>44196</v>
@@ -9258,6 +9280,35 @@
       </c>
       <c r="I78" s="17">
         <v>85913.377697233082</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="12.75">
+      <c r="A79" s="14">
+        <v>46203</v>
+      </c>
+      <c r="B79" s="15">
+        <v>6.2764160156250002</v>
+      </c>
+      <c r="C79" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D79" s="17">
+        <v>318.65319236663788</v>
+      </c>
+      <c r="E79" s="17">
+        <v>40165.447232596714</v>
+      </c>
+      <c r="F79" s="17">
+        <v>252095.05628541086</v>
+      </c>
+      <c r="G79" s="17">
+        <v>154000</v>
+      </c>
+      <c r="H79" s="17">
+        <v>252095.05628541086</v>
+      </c>
+      <c r="I79" s="17">
+        <v>98095.056285410858</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1cn.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="1013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="1033">
   <si>
     <t>PE</t>
   </si>
@@ -4010,6 +4010,90 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">2026/7/1
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/6
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/7
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/8
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/9
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/10
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/13
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/14
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/15
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/16
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/17
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/20
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/21
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/22
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/23
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/24
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/27
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/28
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/7/29
+</t>
+  </si>
+  <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4043,10 +4127,6 @@
   </si>
   <si>
     <t>利润</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -6164,11 +6244,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="460540544"/>
-        <c:axId val="460558720"/>
+        <c:axId val="163213696"/>
+        <c:axId val="163215232"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="460540544"/>
+        <c:axId val="163213696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6211,14 +6291,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460558720"/>
+        <c:crossAx val="163215232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="460558720"/>
+        <c:axId val="163215232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6269,7 +6349,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460540544"/>
+        <c:crossAx val="163213696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6699,31 +6779,31 @@
   <sheetData>
     <row r="1" spans="1:28" s="10" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>997</v>
+        <v>1018</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>998</v>
+        <v>1019</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>999</v>
+        <v>1020</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1000</v>
+        <v>1021</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>1001</v>
+        <v>1022</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>1002</v>
+        <v>1023</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>1003</v>
+        <v>1024</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>1004</v>
+        <v>1025</v>
       </c>
       <c r="I1" s="24" t="s">
-        <v>1005</v>
+        <v>1026</v>
       </c>
       <c r="K1" s="11"/>
     </row>
@@ -6734,7 +6814,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>1012</v>
+        <v>1032</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -6773,25 +6853,25 @@
       </c>
       <c r="J3" s="6"/>
       <c r="L3" s="26" t="s">
-        <v>1006</v>
+        <v>1018</v>
       </c>
       <c r="M3" s="27" t="s">
-        <v>1007</v>
+        <v>1027</v>
       </c>
       <c r="N3" s="27" t="s">
-        <v>1008</v>
+        <v>1028</v>
       </c>
       <c r="O3" s="27" t="s">
-        <v>1004</v>
+        <v>1025</v>
       </c>
       <c r="P3" s="27" t="s">
-        <v>1009</v>
+        <v>1029</v>
       </c>
       <c r="Q3" s="27" t="s">
-        <v>1010</v>
+        <v>1030</v>
       </c>
       <c r="R3" s="27" t="s">
-        <v>1011</v>
+        <v>1031</v>
       </c>
       <c r="T3" s="23">
         <v>44196</v>
@@ -9324,7 +9404,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1270"/>
+  <dimension ref="A1:D1293"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
@@ -28935,7 +29015,7 @@
     </row>
     <row r="1227" spans="1:4">
       <c r="A1227" s="18">
-        <f t="shared" ref="A1227:A1270" si="8">A1226+1</f>
+        <f t="shared" ref="A1227:A1293" si="8">A1226+1</f>
         <v>1225</v>
       </c>
       <c r="B1227" s="30" t="s">
@@ -29635,6 +29715,374 @@
       <c r="D1270" s="18">
         <f>SUM(C$3:C1270)/A1270</f>
         <v>26.574869220600849</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:4">
+      <c r="A1271" s="18">
+        <f t="shared" si="8"/>
+        <v>1269</v>
+      </c>
+      <c r="B1271" s="30" t="s">
+        <v>997</v>
+      </c>
+      <c r="C1271" s="31">
+        <v>41.439998629999998</v>
+      </c>
+      <c r="D1271" s="18">
+        <f>SUM(C$3:C1271)/A1271</f>
+        <v>26.586583270568855</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:4">
+      <c r="A1272" s="18">
+        <f t="shared" si="8"/>
+        <v>1270</v>
+      </c>
+      <c r="B1272" s="30" t="s">
+        <v>998</v>
+      </c>
+      <c r="C1272" s="31">
+        <v>40.11000061</v>
+      </c>
+      <c r="D1272" s="18">
+        <f>SUM(C$3:C1272)/A1272</f>
+        <v>26.597231630678642</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:4">
+      <c r="A1273" s="18">
+        <f t="shared" si="8"/>
+        <v>1271</v>
+      </c>
+      <c r="B1273" s="30" t="s">
+        <v>999</v>
+      </c>
+      <c r="C1273" s="31">
+        <v>40.27999878</v>
+      </c>
+      <c r="D1273" s="18">
+        <f>SUM(C$3:C1273)/A1273</f>
+        <v>26.607996986421622</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:4">
+      <c r="A1274" s="18">
+        <f t="shared" si="8"/>
+        <v>1272</v>
+      </c>
+      <c r="B1274" s="30" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C1274" s="31">
+        <v>39.630001069999999</v>
+      </c>
+      <c r="D1274" s="18">
+        <f>SUM(C$3:C1274)/A1274</f>
+        <v>26.618234411015628</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:4">
+      <c r="A1275" s="18">
+        <f t="shared" si="8"/>
+        <v>1273</v>
+      </c>
+      <c r="B1275" s="30" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C1275" s="31">
+        <v>39.240001679999999</v>
+      </c>
+      <c r="D1275" s="18">
+        <f>SUM(C$3:C1275)/A1275</f>
+        <v>26.628149389231645</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:4">
+      <c r="A1276" s="18">
+        <f t="shared" si="8"/>
+        <v>1274</v>
+      </c>
+      <c r="B1276" s="30" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C1276" s="31">
+        <v>38.680000309999997</v>
+      </c>
+      <c r="D1276" s="18">
+        <f>SUM(C$3:C1276)/A1276</f>
+        <v>26.637609240817802</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:4">
+      <c r="A1277" s="18">
+        <f t="shared" si="8"/>
+        <v>1275</v>
+      </c>
+      <c r="B1277" s="30" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C1277" s="31">
+        <v>40.33000183</v>
+      </c>
+      <c r="D1277" s="18">
+        <f>SUM(C$3:C1277)/A1277</f>
+        <v>26.648348372260298</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:4">
+      <c r="A1278" s="18">
+        <f t="shared" si="8"/>
+        <v>1276</v>
+      </c>
+      <c r="B1278" s="30" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C1278" s="31">
+        <v>38.770000459999999</v>
+      </c>
+      <c r="D1278" s="18">
+        <f>SUM(C$3:C1278)/A1278</f>
+        <v>26.657848099601786</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:4">
+      <c r="A1279" s="18">
+        <f t="shared" si="8"/>
+        <v>1277</v>
+      </c>
+      <c r="B1279" s="30" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C1279" s="31">
+        <v>37.86000061</v>
+      </c>
+      <c r="D1279" s="18">
+        <f>SUM(C$3:C1279)/A1279</f>
+        <v>26.666620341191763</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:4">
+      <c r="A1280" s="18">
+        <f t="shared" si="8"/>
+        <v>1278</v>
+      </c>
+      <c r="B1280" s="30" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C1280" s="31">
+        <v>38.770000459999999</v>
+      </c>
+      <c r="D1280" s="18">
+        <f>SUM(C$3:C1280)/A1280</f>
+        <v>26.676090904665006</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:4">
+      <c r="A1281" s="18">
+        <f t="shared" si="8"/>
+        <v>1279</v>
+      </c>
+      <c r="B1281" s="30" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C1281" s="31">
+        <v>38.490001679999999</v>
+      </c>
+      <c r="D1281" s="18">
+        <f>SUM(C$3:C1281)/A1281</f>
+        <v>26.685327738734856</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:4">
+      <c r="A1282" s="18">
+        <f t="shared" si="8"/>
+        <v>1280</v>
+      </c>
+      <c r="B1282" s="30" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C1282" s="31">
+        <v>37.630001069999999</v>
+      </c>
+      <c r="D1282" s="18">
+        <f>SUM(C$3:C1282)/A1282</f>
+        <v>26.693878264774906</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:4">
+      <c r="A1283" s="18">
+        <f t="shared" si="8"/>
+        <v>1281</v>
+      </c>
+      <c r="B1283" s="30" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C1283" s="31">
+        <v>35.61000061</v>
+      </c>
+      <c r="D1283" s="18">
+        <f>SUM(C$3:C1283)/A1283</f>
+        <v>26.700838547636131</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:4">
+      <c r="A1284" s="18">
+        <f t="shared" si="8"/>
+        <v>1282</v>
+      </c>
+      <c r="B1284" s="30" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C1284" s="31">
+        <v>35.61000061</v>
+      </c>
+      <c r="D1284" s="18">
+        <f>SUM(C$3:C1284)/A1284</f>
+        <v>26.707787972021752</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:4">
+      <c r="A1285" s="18">
+        <f t="shared" si="8"/>
+        <v>1283</v>
+      </c>
+      <c r="B1285" s="30" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C1285" s="31">
+        <v>37.540000919999997</v>
+      </c>
+      <c r="D1285" s="18">
+        <f>SUM(C$3:C1285)/A1285</f>
+        <v>26.716230850391181</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:4">
+      <c r="A1286" s="18">
+        <f t="shared" si="8"/>
+        <v>1284</v>
+      </c>
+      <c r="B1286" s="30" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C1286" s="31">
+        <v>36.959999080000003</v>
+      </c>
+      <c r="D1286" s="18">
+        <f>SUM(C$3:C1286)/A1286</f>
+        <v>26.724208863031063</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:4">
+      <c r="A1287" s="18">
+        <f t="shared" si="8"/>
+        <v>1285</v>
+      </c>
+      <c r="B1287" s="30" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C1287" s="31">
+        <v>37.209999080000003</v>
+      </c>
+      <c r="D1287" s="18">
+        <f>SUM(C$3:C1287)/A1287</f>
+        <v>26.732369011059831</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:4">
+      <c r="A1288" s="18">
+        <f t="shared" si="8"/>
+        <v>1286</v>
+      </c>
+      <c r="B1288" s="30" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C1288" s="31">
+        <v>36.599998470000003</v>
+      </c>
+      <c r="D1288" s="18">
+        <f>SUM(C$3:C1288)/A1288</f>
+        <v>26.740042128835057</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:4">
+      <c r="A1289" s="18">
+        <f t="shared" si="8"/>
+        <v>1287</v>
+      </c>
+      <c r="B1289" s="30" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C1289" s="31">
+        <v>37.66999817</v>
+      </c>
+      <c r="D1289" s="18">
+        <f>SUM(C$3:C1289)/A1289</f>
+        <v>26.74853471317163</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:4">
+      <c r="A1290" s="18">
+        <f t="shared" si="8"/>
+        <v>1288</v>
+      </c>
+      <c r="B1290" s="30" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C1290" s="31">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D1290" s="18">
+        <f>SUM(C$3:C1290)/A1290</f>
+        <v>26.755484609170718</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:4">
+      <c r="A1291" s="18">
+        <f t="shared" si="8"/>
+        <v>1289</v>
+      </c>
+      <c r="B1291" s="30" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C1291" s="31">
+        <v>35.990001679999999</v>
+      </c>
+      <c r="D1291" s="18">
+        <f>SUM(C$3:C1291)/A1291</f>
+        <v>26.762648703096886</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:4">
+      <c r="A1292" s="18">
+        <f t="shared" si="8"/>
+        <v>1290</v>
+      </c>
+      <c r="B1292" s="30">
+        <v>46233</v>
+      </c>
+      <c r="C1292" s="31">
+        <v>34.968000000000004</v>
+      </c>
+      <c r="D1292" s="18">
+        <f>SUM(C$3:C1292)/A1292</f>
+        <v>26.769009440536347</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:4">
+      <c r="A1293" s="18">
+        <f t="shared" si="8"/>
+        <v>1291</v>
+      </c>
+      <c r="B1293" s="30">
+        <v>46234</v>
+      </c>
+      <c r="C1293" s="31">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D1293" s="18">
+        <f>SUM(C$3:C1293)/A1293</f>
+        <v>26.77592732691858</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1cn.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="1034">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="1033">
   <si>
     <t>PE</t>
   </si>
@@ -4127,10 +4127,6 @@
   </si>
   <si>
     <t>利润</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -6266,11 +6262,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="494398848"/>
-        <c:axId val="494734336"/>
+        <c:axId val="352664960"/>
+        <c:axId val="422233216"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="494398848"/>
+        <c:axId val="352664960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6313,14 +6309,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494734336"/>
+        <c:crossAx val="422233216"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="494734336"/>
+        <c:axId val="422233216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6371,7 +6367,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494398848"/>
+        <c:crossAx val="352664960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6836,7 +6832,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -6875,25 +6871,25 @@
       </c>
       <c r="J3" s="6"/>
       <c r="L3" s="26" t="s">
+        <v>1018</v>
+      </c>
+      <c r="M3" s="27" t="s">
         <v>1027</v>
       </c>
-      <c r="M3" s="27" t="s">
+      <c r="N3" s="27" t="s">
         <v>1028</v>
-      </c>
-      <c r="N3" s="27" t="s">
-        <v>1029</v>
       </c>
       <c r="O3" s="27" t="s">
         <v>1025</v>
       </c>
       <c r="P3" s="27" t="s">
+        <v>1029</v>
+      </c>
+      <c r="Q3" s="27" t="s">
         <v>1030</v>
       </c>
-      <c r="Q3" s="27" t="s">
+      <c r="R3" s="27" t="s">
         <v>1031</v>
-      </c>
-      <c r="R3" s="27" t="s">
-        <v>1032</v>
       </c>
       <c r="T3" s="23">
         <v>44196</v>
@@ -9455,7 +9451,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1293"/>
+  <dimension ref="A1:D1314"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
@@ -29066,7 +29062,7 @@
     </row>
     <row r="1227" spans="1:4">
       <c r="A1227" s="18">
-        <f t="shared" ref="A1227:A1293" si="8">A1226+1</f>
+        <f t="shared" ref="A1227:A1314" si="8">A1226+1</f>
         <v>1225</v>
       </c>
       <c r="B1227" s="30" t="s">
@@ -30134,6 +30130,342 @@
       <c r="D1293" s="18">
         <f>SUM(C$3:C1293)/A1293</f>
         <v>26.77592732691858</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:4">
+      <c r="A1294" s="18">
+        <f t="shared" si="8"/>
+        <v>1292</v>
+      </c>
+      <c r="B1294" s="30">
+        <v>46237</v>
+      </c>
+      <c r="C1294" s="31">
+        <v>35.25</v>
+      </c>
+      <c r="D1294" s="18">
+        <f>SUM(C$3:C1294)/A1294</f>
+        <v>26.782486206696507</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:4">
+      <c r="A1295" s="18">
+        <f t="shared" si="8"/>
+        <v>1293</v>
+      </c>
+      <c r="B1295" s="30">
+        <v>46238</v>
+      </c>
+      <c r="C1295" s="31">
+        <v>36.5</v>
+      </c>
+      <c r="D1295" s="18">
+        <f>SUM(C$3:C1295)/A1295</f>
+        <v>26.790001685268283</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:4">
+      <c r="A1296" s="18">
+        <f t="shared" si="8"/>
+        <v>1294</v>
+      </c>
+      <c r="B1296" s="30">
+        <v>46239</v>
+      </c>
+      <c r="C1296" s="31">
+        <v>37.02999878</v>
+      </c>
+      <c r="D1296" s="18">
+        <f>SUM(C$3:C1296)/A1296</f>
+        <v>26.797915129700069</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:4">
+      <c r="A1297" s="18">
+        <f t="shared" si="8"/>
+        <v>1295</v>
+      </c>
+      <c r="B1297" s="30">
+        <v>46240</v>
+      </c>
+      <c r="C1297" s="31">
+        <v>36.75</v>
+      </c>
+      <c r="D1297" s="18">
+        <f>SUM(C$3:C1297)/A1297</f>
+        <v>26.805600137321925</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:4">
+      <c r="A1298" s="18">
+        <f t="shared" si="8"/>
+        <v>1296</v>
+      </c>
+      <c r="B1298" s="30">
+        <v>46241</v>
+      </c>
+      <c r="C1298" s="31">
+        <v>37.130001069999999</v>
+      </c>
+      <c r="D1298" s="18">
+        <f>SUM(C$3:C1298)/A1298</f>
+        <v>26.813566496066272</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:4">
+      <c r="A1299" s="18">
+        <f t="shared" si="8"/>
+        <v>1297</v>
+      </c>
+      <c r="B1299" s="30">
+        <v>46244</v>
+      </c>
+      <c r="C1299" s="31">
+        <v>37.069999690000003</v>
+      </c>
+      <c r="D1299" s="18">
+        <f>SUM(C$3:C1299)/A1299</f>
+        <v>26.821474308860363</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:4">
+      <c r="A1300" s="18">
+        <f t="shared" si="8"/>
+        <v>1298</v>
+      </c>
+      <c r="B1300" s="30">
+        <v>46245</v>
+      </c>
+      <c r="C1300" s="31">
+        <v>36.959999080000003</v>
+      </c>
+      <c r="D1300" s="18">
+        <f>SUM(C$3:C1300)/A1300</f>
+        <v>26.829285190810392</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:4">
+      <c r="A1301" s="18">
+        <f t="shared" si="8"/>
+        <v>1299</v>
+      </c>
+      <c r="B1301" s="30">
+        <v>46246</v>
+      </c>
+      <c r="C1301" s="31">
+        <v>37.380001069999999</v>
+      </c>
+      <c r="D1301" s="18">
+        <f>SUM(C$3:C1301)/A1301</f>
+        <v>26.83740737393525</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:4">
+      <c r="A1302" s="18">
+        <f t="shared" si="8"/>
+        <v>1300</v>
+      </c>
+      <c r="B1302" s="30">
+        <v>46247</v>
+      </c>
+      <c r="C1302" s="31">
+        <v>37.228599549999998</v>
+      </c>
+      <c r="D1302" s="18">
+        <f>SUM(C$3:C1302)/A1302</f>
+        <v>26.845400598686069</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:4">
+      <c r="A1303" s="18">
+        <f t="shared" si="8"/>
+        <v>1301</v>
+      </c>
+      <c r="B1303" s="30">
+        <v>46248</v>
+      </c>
+      <c r="C1303" s="31">
+        <v>37.380001069999999</v>
+      </c>
+      <c r="D1303" s="18">
+        <f>SUM(C$3:C1303)/A1303</f>
+        <v>26.853497908810059</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:4">
+      <c r="A1304" s="18">
+        <f t="shared" si="8"/>
+        <v>1302</v>
+      </c>
+      <c r="B1304" s="30">
+        <v>46251</v>
+      </c>
+      <c r="C1304" s="31">
+        <v>38.369998930000001</v>
+      </c>
+      <c r="D1304" s="18">
+        <f>SUM(C$3:C1304)/A1304</f>
+        <v>26.862343147689622</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:4">
+      <c r="A1305" s="18">
+        <f t="shared" si="8"/>
+        <v>1303</v>
+      </c>
+      <c r="B1305" s="30">
+        <v>46252</v>
+      </c>
+      <c r="C1305" s="31">
+        <v>38.069999690000003</v>
+      </c>
+      <c r="D1305" s="18">
+        <f>SUM(C$3:C1305)/A1305</f>
+        <v>26.870944572511043</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:4">
+      <c r="A1306" s="18">
+        <f t="shared" si="8"/>
+        <v>1304</v>
+      </c>
+      <c r="B1306" s="30">
+        <v>46253</v>
+      </c>
+      <c r="C1306" s="31">
+        <v>35.979999540000001</v>
+      </c>
+      <c r="D1306" s="18">
+        <f>SUM(C$3:C1306)/A1306</f>
+        <v>26.877930044111878</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:4">
+      <c r="A1307" s="18">
+        <f t="shared" si="8"/>
+        <v>1305</v>
+      </c>
+      <c r="B1307" s="30">
+        <v>46254</v>
+      </c>
+      <c r="C1307" s="31">
+        <v>36.099998470000003</v>
+      </c>
+      <c r="D1307" s="18">
+        <f>SUM(C$3:C1307)/A1307</f>
+        <v>26.884996763212179</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:4">
+      <c r="A1308" s="18">
+        <f t="shared" si="8"/>
+        <v>1306</v>
+      </c>
+      <c r="B1308" s="30">
+        <v>46255</v>
+      </c>
+      <c r="C1308" s="31">
+        <v>36.569999690000003</v>
+      </c>
+      <c r="D1308" s="18">
+        <f>SUM(C$3:C1308)/A1308</f>
+        <v>26.892412538806962</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:4">
+      <c r="A1309" s="18">
+        <f t="shared" si="8"/>
+        <v>1307</v>
+      </c>
+      <c r="B1309" s="30">
+        <v>46258</v>
+      </c>
+      <c r="C1309" s="31">
+        <v>35.72000122</v>
+      </c>
+      <c r="D1309" s="18">
+        <f>SUM(C$3:C1309)/A1309</f>
+        <v>26.899166623490352</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:4">
+      <c r="A1310" s="18">
+        <f t="shared" si="8"/>
+        <v>1308</v>
+      </c>
+      <c r="B1310" s="30">
+        <v>46259</v>
+      </c>
+      <c r="C1310" s="31">
+        <v>35.459999080000003</v>
+      </c>
+      <c r="D1310" s="18">
+        <f>SUM(C$3:C1310)/A1310</f>
+        <v>26.905711602432635</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:4">
+      <c r="A1311" s="18">
+        <f t="shared" si="8"/>
+        <v>1309</v>
+      </c>
+      <c r="B1311" s="30">
+        <v>46260</v>
+      </c>
+      <c r="C1311" s="31">
+        <v>35.659999849999998</v>
+      </c>
+      <c r="D1311" s="18">
+        <f>SUM(C$3:C1311)/A1311</f>
+        <v>26.912399370383415</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:4">
+      <c r="A1312" s="18">
+        <f t="shared" si="8"/>
+        <v>1310</v>
+      </c>
+      <c r="B1312" s="30">
+        <v>46261</v>
+      </c>
+      <c r="C1312" s="31">
+        <v>36.069999690000003</v>
+      </c>
+      <c r="D1312" s="18">
+        <f>SUM(C$3:C1312)/A1312</f>
+        <v>26.919389904978544</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:4">
+      <c r="A1313" s="18">
+        <f t="shared" si="8"/>
+        <v>1311</v>
+      </c>
+      <c r="B1313" s="30">
+        <v>46262</v>
+      </c>
+      <c r="C1313" s="31">
+        <v>35.740001679999999</v>
+      </c>
+      <c r="D1313" s="18">
+        <f>SUM(C$3:C1313)/A1313</f>
+        <v>26.926118060413344</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:4">
+      <c r="A1314" s="18">
+        <f t="shared" si="8"/>
+        <v>1312</v>
+      </c>
+      <c r="B1314" s="30">
+        <v>46265</v>
+      </c>
+      <c r="C1314" s="31">
+        <v>35.77999878</v>
+      </c>
+      <c r="D1314" s="18">
+        <f>SUM(C$3:C1314)/A1314</f>
+        <v>26.932866445108154</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1cn.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="1033">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="1034">
   <si>
     <t>PE</t>
   </si>
@@ -4127,6 +4127,10 @@
   </si>
   <si>
     <t>利润</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4726,7 +4730,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="78"/>
+                <c:ptCount val="79"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4960,6 +4964,9 @@
                 </c:pt>
                 <c:pt idx="77">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4969,7 +4976,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="78"/>
+                <c:ptCount val="79"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5203,6 +5210,9 @@
                 </c:pt>
                 <c:pt idx="77">
                   <c:v>156000</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>158000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5245,7 +5255,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="78"/>
+                <c:ptCount val="79"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5479,6 +5489,9 @@
                 </c:pt>
                 <c:pt idx="77">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5488,7 +5501,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="78"/>
+                <c:ptCount val="79"/>
                 <c:pt idx="0">
                   <c:v>2000.0000000000002</c:v>
                 </c:pt>
@@ -5722,6 +5735,9 @@
                 </c:pt>
                 <c:pt idx="77">
                   <c:v>212367.41242229048</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>216089.9404344116</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5764,7 +5780,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="78"/>
+                <c:ptCount val="79"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5998,6 +6014,9 @@
                 </c:pt>
                 <c:pt idx="77">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6007,7 +6026,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="78"/>
+                <c:ptCount val="79"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6241,6 +6260,9 @@
                 </c:pt>
                 <c:pt idx="77">
                   <c:v>56367.412422290479</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>58089.940434411605</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6262,11 +6284,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="352664960"/>
-        <c:axId val="422233216"/>
+        <c:axId val="367668608"/>
+        <c:axId val="367670400"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="352664960"/>
+        <c:axId val="367668608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6309,14 +6331,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="422233216"/>
+        <c:crossAx val="367670400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="422233216"/>
+        <c:axId val="367670400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6367,7 +6389,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="352664960"/>
+        <c:crossAx val="367668608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6773,7 +6795,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB80"/>
+  <dimension ref="A1:AB81"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -6832,7 +6854,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -6871,25 +6893,25 @@
       </c>
       <c r="J3" s="6"/>
       <c r="L3" s="26" t="s">
-        <v>1018</v>
+        <v>1027</v>
       </c>
       <c r="M3" s="27" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="N3" s="27" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="O3" s="27" t="s">
         <v>1025</v>
       </c>
       <c r="P3" s="27" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="Q3" s="27" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="R3" s="27" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="T3" s="23">
         <v>44196</v>
@@ -9436,6 +9458,35 @@
       </c>
       <c r="I80" s="17">
         <v>56367.412422290479</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="12.75">
+      <c r="A81" s="14">
+        <v>46265</v>
+      </c>
+      <c r="B81" s="15">
+        <v>5.2800039062500002</v>
+      </c>
+      <c r="C81" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D81" s="17">
+        <v>378.78759855320891</v>
+      </c>
+      <c r="E81" s="17">
+        <v>40926.094804328364</v>
+      </c>
+      <c r="F81" s="17">
+        <v>216089.9404344116</v>
+      </c>
+      <c r="G81" s="17">
+        <v>158000</v>
+      </c>
+      <c r="H81" s="17">
+        <v>216089.9404344116</v>
+      </c>
+      <c r="I81" s="17">
+        <v>58089.940434411605</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1cn.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="1034">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="1033">
   <si>
     <t>PE</t>
   </si>
@@ -4127,10 +4127,6 @@
   </si>
   <si>
     <t>利润</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -6284,11 +6280,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="367668608"/>
-        <c:axId val="367670400"/>
+        <c:axId val="464887168"/>
+        <c:axId val="423691392"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="367668608"/>
+        <c:axId val="464887168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6331,14 +6327,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="367670400"/>
+        <c:crossAx val="423691392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="367670400"/>
+        <c:axId val="423691392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6389,7 +6385,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="367668608"/>
+        <c:crossAx val="464887168"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6854,7 +6850,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -6893,25 +6889,25 @@
       </c>
       <c r="J3" s="6"/>
       <c r="L3" s="26" t="s">
+        <v>1018</v>
+      </c>
+      <c r="M3" s="27" t="s">
         <v>1027</v>
       </c>
-      <c r="M3" s="27" t="s">
+      <c r="N3" s="27" t="s">
         <v>1028</v>
-      </c>
-      <c r="N3" s="27" t="s">
-        <v>1029</v>
       </c>
       <c r="O3" s="27" t="s">
         <v>1025</v>
       </c>
       <c r="P3" s="27" t="s">
+        <v>1029</v>
+      </c>
+      <c r="Q3" s="27" t="s">
         <v>1030</v>
       </c>
-      <c r="Q3" s="27" t="s">
+      <c r="R3" s="27" t="s">
         <v>1031</v>
-      </c>
-      <c r="R3" s="27" t="s">
-        <v>1032</v>
       </c>
       <c r="T3" s="23">
         <v>44196</v>
@@ -9502,7 +9498,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1314"/>
+  <dimension ref="A1:D1335"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
@@ -29113,7 +29109,7 @@
     </row>
     <row r="1227" spans="1:4">
       <c r="A1227" s="18">
-        <f t="shared" ref="A1227:A1314" si="8">A1226+1</f>
+        <f t="shared" ref="A1227:A1335" si="8">A1226+1</f>
         <v>1225</v>
       </c>
       <c r="B1227" s="30" t="s">
@@ -30517,6 +30513,342 @@
       <c r="D1314" s="18">
         <f>SUM(C$3:C1314)/A1314</f>
         <v>26.932866445108154</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:4">
+      <c r="A1315" s="18">
+        <f t="shared" si="8"/>
+        <v>1313</v>
+      </c>
+      <c r="B1315" s="30">
+        <v>46266</v>
+      </c>
+      <c r="C1315" s="31">
+        <v>31.86000061</v>
+      </c>
+      <c r="D1315" s="18">
+        <f>SUM(C$3:C1315)/A1315</f>
+        <v>26.936619022537624</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:4">
+      <c r="A1316" s="18">
+        <f t="shared" si="8"/>
+        <v>1314</v>
+      </c>
+      <c r="B1316" s="30">
+        <v>46267</v>
+      </c>
+      <c r="C1316" s="31">
+        <v>31.18000031</v>
+      </c>
+      <c r="D1316" s="18">
+        <f>SUM(C$3:C1316)/A1316</f>
+        <v>26.93984838424802</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:4">
+      <c r="A1317" s="18">
+        <f t="shared" si="8"/>
+        <v>1315</v>
+      </c>
+      <c r="B1317" s="30">
+        <v>46268</v>
+      </c>
+      <c r="C1317" s="31">
+        <v>31.18000031</v>
+      </c>
+      <c r="D1317" s="18">
+        <f>SUM(C$3:C1317)/A1317</f>
+        <v>26.94307283438167</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:4">
+      <c r="A1318" s="18">
+        <f t="shared" si="8"/>
+        <v>1316</v>
+      </c>
+      <c r="B1318" s="30">
+        <v>46269</v>
+      </c>
+      <c r="C1318" s="31">
+        <v>30.870000839999999</v>
+      </c>
+      <c r="D1318" s="18">
+        <f>SUM(C$3:C1318)/A1318</f>
+        <v>26.946056822227884</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:4">
+      <c r="A1319" s="18">
+        <f t="shared" si="8"/>
+        <v>1317</v>
+      </c>
+      <c r="B1319" s="30">
+        <v>46272</v>
+      </c>
+      <c r="C1319" s="31">
+        <v>31.600000380000001</v>
+      </c>
+      <c r="D1319" s="18">
+        <f>SUM(C$3:C1319)/A1319</f>
+        <v>26.949590568285419</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:4">
+      <c r="A1320" s="18">
+        <f t="shared" si="8"/>
+        <v>1318</v>
+      </c>
+      <c r="B1320" s="30">
+        <v>46273</v>
+      </c>
+      <c r="C1320" s="31">
+        <v>31.219999309999999</v>
+      </c>
+      <c r="D1320" s="18">
+        <f>SUM(C$3:C1320)/A1320</f>
+        <v>26.952830635616007</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:4">
+      <c r="A1321" s="18">
+        <f t="shared" si="8"/>
+        <v>1319</v>
+      </c>
+      <c r="B1321" s="30">
+        <v>46274</v>
+      </c>
+      <c r="C1321" s="31">
+        <v>31.200000760000002</v>
+      </c>
+      <c r="D1321" s="18">
+        <f>SUM(C$3:C1321)/A1321</f>
+        <v>26.956050628128807</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:4">
+      <c r="A1322" s="18">
+        <f t="shared" si="8"/>
+        <v>1320</v>
+      </c>
+      <c r="B1322" s="30">
+        <v>46275</v>
+      </c>
+      <c r="C1322" s="31">
+        <v>30.920000080000001</v>
+      </c>
+      <c r="D1322" s="18">
+        <f>SUM(C$3:C1322)/A1322</f>
+        <v>26.959053620137798</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:4">
+      <c r="A1323" s="18">
+        <f t="shared" si="8"/>
+        <v>1321</v>
+      </c>
+      <c r="B1323" s="30">
+        <v>46276</v>
+      </c>
+      <c r="C1323" s="31">
+        <v>30.739999770000001</v>
+      </c>
+      <c r="D1323" s="18">
+        <f>SUM(C$3:C1323)/A1323</f>
+        <v>26.961915804959798</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:4">
+      <c r="A1324" s="18">
+        <f t="shared" si="8"/>
+        <v>1322</v>
+      </c>
+      <c r="B1324" s="30">
+        <v>46279</v>
+      </c>
+      <c r="C1324" s="31">
+        <v>30.61000061</v>
+      </c>
+      <c r="D1324" s="18">
+        <f>SUM(C$3:C1324)/A1324</f>
+        <v>26.964675324479497</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:4">
+      <c r="A1325" s="18">
+        <f t="shared" si="8"/>
+        <v>1323</v>
+      </c>
+      <c r="B1325" s="30">
+        <v>46280</v>
+      </c>
+      <c r="C1325" s="31">
+        <v>30.219999309999999</v>
+      </c>
+      <c r="D1325" s="18">
+        <f>SUM(C$3:C1325)/A1325</f>
+        <v>26.967135886826828</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:4">
+      <c r="A1326" s="18">
+        <f t="shared" si="8"/>
+        <v>1324</v>
+      </c>
+      <c r="B1326" s="30">
+        <v>46281</v>
+      </c>
+      <c r="C1326" s="31">
+        <v>30.56999969</v>
+      </c>
+      <c r="D1326" s="18">
+        <f>SUM(C$3:C1326)/A1326</f>
+        <v>26.969857083052791</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:4">
+      <c r="A1327" s="18">
+        <f t="shared" si="8"/>
+        <v>1325</v>
+      </c>
+      <c r="B1327" s="30">
+        <v>46282</v>
+      </c>
+      <c r="C1327" s="31">
+        <v>30.530000690000001</v>
+      </c>
+      <c r="D1327" s="18">
+        <f>SUM(C$3:C1327)/A1327</f>
+        <v>26.972543983888222</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:4">
+      <c r="A1328" s="18">
+        <f t="shared" si="8"/>
+        <v>1326</v>
+      </c>
+      <c r="B1328" s="30">
+        <v>46283</v>
+      </c>
+      <c r="C1328" s="31">
+        <v>30.989999770000001</v>
+      </c>
+      <c r="D1328" s="18">
+        <f>SUM(C$3:C1328)/A1328</f>
+        <v>26.975573739383027</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:4">
+      <c r="A1329" s="18">
+        <f t="shared" si="8"/>
+        <v>1327</v>
+      </c>
+      <c r="B1329" s="30">
+        <v>46286</v>
+      </c>
+      <c r="C1329" s="31">
+        <v>31.049999239999998</v>
+      </c>
+      <c r="D1329" s="18">
+        <f>SUM(C$3:C1329)/A1329</f>
+        <v>26.978644142925315</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:4">
+      <c r="A1330" s="18">
+        <f t="shared" si="8"/>
+        <v>1328</v>
+      </c>
+      <c r="B1330" s="30">
+        <v>46287</v>
+      </c>
+      <c r="C1330" s="31">
+        <v>31.120000839999999</v>
+      </c>
+      <c r="D1330" s="18">
+        <f>SUM(C$3:C1330)/A1330</f>
+        <v>26.981762634414071</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:4">
+      <c r="A1331" s="18">
+        <f t="shared" si="8"/>
+        <v>1329</v>
+      </c>
+      <c r="B1331" s="30">
+        <v>46288</v>
+      </c>
+      <c r="C1331" s="31">
+        <v>30.93000031</v>
+      </c>
+      <c r="D1331" s="18">
+        <f>SUM(C$3:C1331)/A1331</f>
+        <v>26.984733467879526</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:4">
+      <c r="A1332" s="18">
+        <f t="shared" si="8"/>
+        <v>1330</v>
+      </c>
+      <c r="B1332" s="30">
+        <v>46289</v>
+      </c>
+      <c r="C1332" s="31">
+        <v>30.200000760000002</v>
+      </c>
+      <c r="D1332" s="18">
+        <f>SUM(C$3:C1332)/A1332</f>
+        <v>26.987150962084126</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:4">
+      <c r="A1333" s="18">
+        <f t="shared" si="8"/>
+        <v>1331</v>
+      </c>
+      <c r="B1333" s="30">
+        <v>46293</v>
+      </c>
+      <c r="C1333" s="31">
+        <v>29.11000061</v>
+      </c>
+      <c r="D1333" s="18">
+        <f>SUM(C$3:C1333)/A1333</f>
+        <v>26.988745890444697</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:4">
+      <c r="A1334" s="18">
+        <f t="shared" si="8"/>
+        <v>1332</v>
+      </c>
+      <c r="B1334" s="30">
+        <v>46294</v>
+      </c>
+      <c r="C1334" s="31">
+        <v>29.059999470000001</v>
+      </c>
+      <c r="D1334" s="18">
+        <f>SUM(C$3:C1334)/A1334</f>
+        <v>26.990300885624546</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:4">
+      <c r="A1335" s="18">
+        <f t="shared" si="8"/>
+        <v>1333</v>
+      </c>
+      <c r="B1335" s="30">
+        <v>46295</v>
+      </c>
+      <c r="C1335" s="31">
+        <v>29.059999470000001</v>
+      </c>
+      <c r="D1335" s="18">
+        <f>SUM(C$3:C1335)/A1335</f>
+        <v>26.991853547728354</v>
       </c>
     </row>
   </sheetData>
